--- a/Decks/Kumena.xlsx
+++ b/Decks/Kumena.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75327599-8454-4AEF-A48E-2213F8672802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63CD93D-BD9C-46C0-BC59-05E06F0D16F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2DDDE493-6491-4DA6-9A01-72FF3C603222}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{2DDDE493-6491-4DA6-9A01-72FF3C603222}"/>
   </bookViews>
   <sheets>
     <sheet name="Kumena" sheetId="1" r:id="rId1"/>
@@ -203,9 +203,6 @@
     <t>Merfolk Mistbinder</t>
   </si>
   <si>
-    <t>Deeprooot Wayfinder</t>
-  </si>
-  <si>
     <t>Lord of Atlantis</t>
   </si>
   <si>
@@ -315,6 +312,9 @@
   </si>
   <si>
     <t>Mindspring Merfolk</t>
+  </si>
+  <si>
+    <t>Deeproot Wayfinder</t>
   </si>
 </sst>
 </file>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="C68" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D68" t="s">
         <v>55</v>
-      </c>
-      <c r="D68" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1750,10 +1750,10 @@
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1765,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D70" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1780,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D71" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -1795,10 +1795,10 @@
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D72" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -1810,10 +1810,10 @@
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D73" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -1825,10 +1825,10 @@
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D74" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -1840,10 +1840,10 @@
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D75" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -1855,10 +1855,10 @@
         <v>0</v>
       </c>
       <c r="C76" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D76" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -1870,10 +1870,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D77" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -1885,10 +1885,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D79" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1915,10 +1915,10 @@
         <v>0</v>
       </c>
       <c r="C80" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D80" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D81" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -1945,10 +1945,10 @@
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D82" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -1960,10 +1960,10 @@
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -1975,10 +1975,10 @@
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D84" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -1990,10 +1990,10 @@
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D85" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -2005,235 +2005,235 @@
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>74</v>
+      </c>
+      <c r="B87" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C87" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B87" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="D87" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D88" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D89" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D90" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D91" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D92" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D93" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>82</v>
+      </c>
+      <c r="B94" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B94" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="D94" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D95" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D96" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D97" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D98" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D99" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D100" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D101" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Kumena.xlsx
+++ b/Decks/Kumena.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63CD93D-BD9C-46C0-BC59-05E06F0D16F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C703232A-F710-4660-A4BF-5E0607FAE5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{2DDDE493-6491-4DA6-9A01-72FF3C603222}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2DDDE493-6491-4DA6-9A01-72FF3C603222}"/>
   </bookViews>
   <sheets>
     <sheet name="Kumena" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="94">
   <si>
     <t>Função</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>Deeproot Wayfinder</t>
+  </si>
+  <si>
+    <t>Dreamroot Cascade</t>
   </si>
 </sst>
 </file>
@@ -864,10 +867,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
